--- a/Nuevos DeepWins/Problem4_Bullseye5/Res/Comparativa_6_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem4_Bullseye5/Res/Comparativa_6_Neuronas.xlsx
@@ -581,42 +581,42 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.20802</v>
+        <v>0.188152</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.475232</v>
+        <v>0.61</v>
       </c>
       <c r="H2" t="n">
-        <v>0.481191</v>
+        <v>0.478056</v>
       </c>
       <c r="I2" t="n">
-        <v>0.478193</v>
+        <v>0.5360279999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.211148</v>
+        <v>0.187072</v>
       </c>
       <c r="K2" t="n">
-        <v>0.516556</v>
+        <v>0.592</v>
       </c>
       <c r="L2" t="n">
-        <v>0.458824</v>
+        <v>0.435294</v>
       </c>
       <c r="M2" t="n">
-        <v>0.485981</v>
+        <v>0.501695</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_5.txt</t>
+          <t>_2_6_1_1790731720_12.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>6</v>
       </c>
       <c r="AA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.187828</v>
+        <v>0.190486</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -699,25 +699,25 @@
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.616105</v>
+        <v>0.606285</v>
       </c>
       <c r="H3" t="n">
-        <v>0.515674</v>
+        <v>0.514107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.561433</v>
+        <v>0.556404</v>
       </c>
       <c r="J3" t="n">
-        <v>0.186825</v>
+        <v>0.190133</v>
       </c>
       <c r="K3" t="n">
-        <v>0.61194</v>
+        <v>0.598485</v>
       </c>
       <c r="L3" t="n">
-        <v>0.482353</v>
+        <v>0.464706</v>
       </c>
       <c r="M3" t="n">
-        <v>0.539474</v>
+        <v>0.5231789999999999</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_15.txt</t>
+          <t>_2_6_1_1790731720_9.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.179242</v>
+        <v>0.191455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.56259</v>
+        <v>0.534629</v>
       </c>
       <c r="H4" t="n">
-        <v>0.612853</v>
+        <v>0.689655</v>
       </c>
       <c r="I4" t="n">
-        <v>0.586647</v>
+        <v>0.6023269999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.181026</v>
+        <v>0.190092</v>
       </c>
       <c r="K4" t="n">
-        <v>0.562874</v>
+        <v>0.576355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.552941</v>
+        <v>0.688235</v>
       </c>
       <c r="M4" t="n">
-        <v>0.557864</v>
+        <v>0.627346</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,23 +854,23 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_8.txt</t>
+          <t>_2_6_1_1790731720_11.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>6</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -884,7 +884,7 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.190155</v>
+        <v>0.192539</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.516332</v>
+        <v>0.601363</v>
       </c>
       <c r="H5" t="n">
-        <v>0.644201</v>
+        <v>0.553292</v>
       </c>
       <c r="I5" t="n">
-        <v>0.573222</v>
+        <v>0.576327</v>
       </c>
       <c r="J5" t="n">
-        <v>0.188937</v>
+        <v>0.195856</v>
       </c>
       <c r="K5" t="n">
-        <v>0.550505</v>
+        <v>0.593103</v>
       </c>
       <c r="L5" t="n">
-        <v>0.641176</v>
+        <v>0.5058820000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.592391</v>
+        <v>0.546032</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_4.txt</t>
+          <t>_2_6_1_1790731720_14.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -985,42 +985,42 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.193349</v>
+        <v>0.199885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.528325</v>
+        <v>0.50828</v>
       </c>
       <c r="H6" t="n">
-        <v>0.672414</v>
+        <v>0.6253919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.591724</v>
+        <v>0.560787</v>
       </c>
       <c r="J6" t="n">
-        <v>0.19347</v>
+        <v>0.201084</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5612239999999999</v>
+        <v>0.536842</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6470590000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.601093</v>
+        <v>0.566667</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_0.txt</t>
+          <t>_2_6_1_1790731720_5.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>6</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1086,42 +1086,42 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.192098</v>
+        <v>0.191088</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.606742</v>
+        <v>0.548159</v>
       </c>
       <c r="H7" t="n">
-        <v>0.507837</v>
+        <v>0.606583</v>
       </c>
       <c r="I7" t="n">
-        <v>0.552901</v>
+        <v>0.575893</v>
       </c>
       <c r="J7" t="n">
-        <v>0.190562</v>
+        <v>0.194727</v>
       </c>
       <c r="K7" t="n">
-        <v>0.589552</v>
+        <v>0.569767</v>
       </c>
       <c r="L7" t="n">
-        <v>0.464706</v>
+        <v>0.576471</v>
       </c>
       <c r="M7" t="n">
-        <v>0.519737</v>
+        <v>0.573099</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,23 +1157,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_17.txt</t>
+          <t>_2_3_3_1_1790731769_9.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>6</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1187,42 +1187,42 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.19791</v>
+        <v>0.193022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.494695</v>
+        <v>0.523632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.584639</v>
+        <v>0.659875</v>
       </c>
       <c r="I8" t="n">
-        <v>0.535919</v>
+        <v>0.583911</v>
       </c>
       <c r="J8" t="n">
-        <v>0.197199</v>
+        <v>0.191672</v>
       </c>
       <c r="K8" t="n">
-        <v>0.535519</v>
+        <v>0.565657</v>
       </c>
       <c r="L8" t="n">
-        <v>0.576471</v>
+        <v>0.658824</v>
       </c>
       <c r="M8" t="n">
-        <v>0.555241</v>
+        <v>0.608696</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,23 +1258,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_11.txt</t>
+          <t>_2_6_1_1790731720_3.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>6</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1288,7 +1288,7 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.212153</v>
+        <v>0.194212</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.502732</v>
+        <v>0.53911</v>
       </c>
       <c r="H9" t="n">
-        <v>0.432602</v>
+        <v>0.702194</v>
       </c>
       <c r="I9" t="n">
-        <v>0.465038</v>
+        <v>0.609939</v>
       </c>
       <c r="J9" t="n">
-        <v>0.213777</v>
+        <v>0.195569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.528169</v>
+        <v>0.574257</v>
       </c>
       <c r="L9" t="n">
-        <v>0.441176</v>
+        <v>0.682353</v>
       </c>
       <c r="M9" t="n">
-        <v>0.480769</v>
+        <v>0.623656</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_14.txt</t>
+          <t>_2_3_3_1_1790731769_15.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.190486</v>
+        <v>0.189438</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.606285</v>
+        <v>0.608939</v>
       </c>
       <c r="H10" t="n">
-        <v>0.514107</v>
+        <v>0.512539</v>
       </c>
       <c r="I10" t="n">
-        <v>0.556404</v>
+        <v>0.556596</v>
       </c>
       <c r="J10" t="n">
-        <v>0.190133</v>
+        <v>0.188568</v>
       </c>
       <c r="K10" t="n">
-        <v>0.598485</v>
+        <v>0.5954199999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.464706</v>
+        <v>0.458824</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5231789999999999</v>
+        <v>0.518272</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_9.txt</t>
+          <t>_2_6_1_1790731720_6.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1490,42 +1490,42 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.209246</v>
+        <v>0.192426</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.498344</v>
+        <v>0.6192</v>
       </c>
       <c r="H11" t="n">
-        <v>0.471787</v>
+        <v>0.606583</v>
       </c>
       <c r="I11" t="n">
-        <v>0.484702</v>
+        <v>0.612827</v>
       </c>
       <c r="J11" t="n">
-        <v>0.213499</v>
+        <v>0.196411</v>
       </c>
       <c r="K11" t="n">
-        <v>0.534247</v>
+        <v>0.641026</v>
       </c>
       <c r="L11" t="n">
-        <v>0.458824</v>
+        <v>0.588235</v>
       </c>
       <c r="M11" t="n">
-        <v>0.493671</v>
+        <v>0.613497</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,23 +1561,23 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_6.txt</t>
+          <t>_2_6_1_1790731720_8.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z11" t="n">
         <v>6</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.191102</v>
+        <v>0.212153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.545588</v>
+        <v>0.502732</v>
       </c>
       <c r="H12" t="n">
-        <v>0.581505</v>
+        <v>0.432602</v>
       </c>
       <c r="I12" t="n">
-        <v>0.562974</v>
+        <v>0.465038</v>
       </c>
       <c r="J12" t="n">
-        <v>0.193516</v>
+        <v>0.213777</v>
       </c>
       <c r="K12" t="n">
-        <v>0.590909</v>
+        <v>0.528169</v>
       </c>
       <c r="L12" t="n">
-        <v>0.535294</v>
+        <v>0.441176</v>
       </c>
       <c r="M12" t="n">
-        <v>0.561728</v>
+        <v>0.480769</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_19.txt</t>
+          <t>_2_3_3_1_1790731769_14.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,42 +1692,42 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.188152</v>
+        <v>0.209498</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.61</v>
+        <v>0.494078</v>
       </c>
       <c r="H13" t="n">
-        <v>0.478056</v>
+        <v>0.45768</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5360279999999999</v>
+        <v>0.475183</v>
       </c>
       <c r="J13" t="n">
-        <v>0.187072</v>
+        <v>0.208328</v>
       </c>
       <c r="K13" t="n">
-        <v>0.592</v>
+        <v>0.528169</v>
       </c>
       <c r="L13" t="n">
-        <v>0.435294</v>
+        <v>0.441176</v>
       </c>
       <c r="M13" t="n">
-        <v>0.501695</v>
+        <v>0.480769</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,23 +1763,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_12.txt</t>
+          <t>_2_3_3_1_1790731769_17.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z13" t="n">
         <v>6</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.19965</v>
+        <v>0.212392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1810,25 +1810,25 @@
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.501992</v>
+        <v>0.497537</v>
       </c>
       <c r="H14" t="n">
-        <v>0.592476</v>
+        <v>0.474922</v>
       </c>
       <c r="I14" t="n">
-        <v>0.543494</v>
+        <v>0.485966</v>
       </c>
       <c r="J14" t="n">
-        <v>0.201776</v>
+        <v>0.221213</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5251400000000001</v>
+        <v>0.539007</v>
       </c>
       <c r="L14" t="n">
-        <v>0.552941</v>
+        <v>0.447059</v>
       </c>
       <c r="M14" t="n">
-        <v>0.538682</v>
+        <v>0.488746</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_18.txt</t>
+          <t>_2_3_3_1_1790731769_13.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.189665</v>
+        <v>0.196115</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.606498</v>
+        <v>0.542222</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5266459999999999</v>
+        <v>0.573668</v>
       </c>
       <c r="I15" t="n">
-        <v>0.563758</v>
+        <v>0.5575020000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.190911</v>
+        <v>0.194178</v>
       </c>
       <c r="K15" t="n">
-        <v>0.643411</v>
+        <v>0.5786520000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.488235</v>
+        <v>0.605882</v>
       </c>
       <c r="M15" t="n">
-        <v>0.555184</v>
+        <v>0.591954</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_7.txt</t>
+          <t>_2_6_1_1790731720_13.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.199613</v>
+        <v>0.212559</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2012,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.526536</v>
+        <v>0.507168</v>
       </c>
       <c r="H16" t="n">
-        <v>0.590909</v>
+        <v>0.443574</v>
       </c>
       <c r="I16" t="n">
-        <v>0.556868</v>
+        <v>0.473244</v>
       </c>
       <c r="J16" t="n">
-        <v>0.201073</v>
+        <v>0.214107</v>
       </c>
       <c r="K16" t="n">
-        <v>0.556818</v>
+        <v>0.522388</v>
       </c>
       <c r="L16" t="n">
-        <v>0.576471</v>
+        <v>0.411765</v>
       </c>
       <c r="M16" t="n">
-        <v>0.566474</v>
+        <v>0.460526</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_12.txt</t>
+          <t>_2_3_3_1_1790731769_16.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.212392</v>
+        <v>0.204732</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.497537</v>
+        <v>0.506912</v>
       </c>
       <c r="H17" t="n">
-        <v>0.474922</v>
+        <v>0.517241</v>
       </c>
       <c r="I17" t="n">
-        <v>0.485966</v>
+        <v>0.512025</v>
       </c>
       <c r="J17" t="n">
-        <v>0.221213</v>
+        <v>0.201816</v>
       </c>
       <c r="K17" t="n">
-        <v>0.539007</v>
+        <v>0.538961</v>
       </c>
       <c r="L17" t="n">
-        <v>0.447059</v>
+        <v>0.488235</v>
       </c>
       <c r="M17" t="n">
-        <v>0.488746</v>
+        <v>0.512346</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_13.txt</t>
+          <t>_2_3_3_1_1790731769_4.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2197,7 +2197,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.194212</v>
+        <v>0.213079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2214,25 +2214,25 @@
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.53911</v>
+        <v>0.499069</v>
       </c>
       <c r="H18" t="n">
-        <v>0.702194</v>
+        <v>0.420063</v>
       </c>
       <c r="I18" t="n">
-        <v>0.609939</v>
+        <v>0.45617</v>
       </c>
       <c r="J18" t="n">
-        <v>0.195569</v>
+        <v>0.215386</v>
       </c>
       <c r="K18" t="n">
-        <v>0.574257</v>
+        <v>0.511278</v>
       </c>
       <c r="L18" t="n">
-        <v>0.682353</v>
+        <v>0.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0.623656</v>
+        <v>0.448845</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_15.txt</t>
+          <t>_2_3_3_1_1790731769_10.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2298,42 +2298,42 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.190124</v>
+        <v>0.209246</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.598604</v>
+        <v>0.498344</v>
       </c>
       <c r="H19" t="n">
-        <v>0.537618</v>
+        <v>0.471787</v>
       </c>
       <c r="I19" t="n">
-        <v>0.566474</v>
+        <v>0.484702</v>
       </c>
       <c r="J19" t="n">
-        <v>0.19043</v>
+        <v>0.213499</v>
       </c>
       <c r="K19" t="n">
-        <v>0.594406</v>
+        <v>0.534247</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.458824</v>
       </c>
       <c r="M19" t="n">
-        <v>0.543131</v>
+        <v>0.493671</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,23 +2369,23 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_0.txt</t>
+          <t>_2_3_3_1_1790731769_6.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z19" t="n">
         <v>6</v>
       </c>
       <c r="AA19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.192539</v>
+        <v>0.190155</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2416,25 +2416,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.601363</v>
+        <v>0.516332</v>
       </c>
       <c r="H20" t="n">
-        <v>0.553292</v>
+        <v>0.644201</v>
       </c>
       <c r="I20" t="n">
-        <v>0.576327</v>
+        <v>0.573222</v>
       </c>
       <c r="J20" t="n">
-        <v>0.195856</v>
+        <v>0.188937</v>
       </c>
       <c r="K20" t="n">
-        <v>0.593103</v>
+        <v>0.550505</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5058820000000001</v>
+        <v>0.641176</v>
       </c>
       <c r="M20" t="n">
-        <v>0.546032</v>
+        <v>0.592391</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_14.txt</t>
+          <t>_2_6_1_1790731720_4.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2500,42 +2500,42 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.20234</v>
+        <v>0.189665</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E21" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.490223</v>
+        <v>0.606498</v>
       </c>
       <c r="H21" t="n">
-        <v>0.550157</v>
+        <v>0.5266459999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.518464</v>
+        <v>0.563758</v>
       </c>
       <c r="J21" t="n">
-        <v>0.204362</v>
+        <v>0.190911</v>
       </c>
       <c r="K21" t="n">
-        <v>0.533708</v>
+        <v>0.643411</v>
       </c>
       <c r="L21" t="n">
-        <v>0.558824</v>
+        <v>0.488235</v>
       </c>
       <c r="M21" t="n">
-        <v>0.545977</v>
+        <v>0.555184</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,23 +2571,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_19.txt</t>
+          <t>_2_6_1_1790731720_7.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>6</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2601,42 +2601,42 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.204732</v>
+        <v>0.188427</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E22" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.506912</v>
+        <v>0.604356</v>
       </c>
       <c r="H22" t="n">
-        <v>0.517241</v>
+        <v>0.521944</v>
       </c>
       <c r="I22" t="n">
-        <v>0.512025</v>
+        <v>0.560135</v>
       </c>
       <c r="J22" t="n">
-        <v>0.201816</v>
+        <v>0.186991</v>
       </c>
       <c r="K22" t="n">
-        <v>0.538961</v>
+        <v>0.6</v>
       </c>
       <c r="L22" t="n">
-        <v>0.488235</v>
+        <v>0.494118</v>
       </c>
       <c r="M22" t="n">
-        <v>0.512346</v>
+        <v>0.541936</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_4.txt</t>
+          <t>_2_6_1_1790731720_1.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>6</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2702,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.188288</v>
+        <v>0.187828</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E23" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.549412</v>
+        <v>0.616105</v>
       </c>
       <c r="H23" t="n">
-        <v>0.731975</v>
+        <v>0.515674</v>
       </c>
       <c r="I23" t="n">
-        <v>0.627688</v>
+        <v>0.561433</v>
       </c>
       <c r="J23" t="n">
-        <v>0.188066</v>
+        <v>0.186825</v>
       </c>
       <c r="K23" t="n">
-        <v>0.59434</v>
+        <v>0.61194</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7411759999999999</v>
+        <v>0.482353</v>
       </c>
       <c r="M23" t="n">
-        <v>0.659686</v>
+        <v>0.539474</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,23 +2773,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_3.txt</t>
+          <t>_2_6_1_1790731720_15.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>6</v>
       </c>
       <c r="AA23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2803,42 +2803,42 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.194461</v>
+        <v>0.192098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E24" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.52381</v>
+        <v>0.606742</v>
       </c>
       <c r="H24" t="n">
-        <v>0.637931</v>
+        <v>0.507837</v>
       </c>
       <c r="I24" t="n">
-        <v>0.575265</v>
+        <v>0.552901</v>
       </c>
       <c r="J24" t="n">
-        <v>0.196644</v>
+        <v>0.190562</v>
       </c>
       <c r="K24" t="n">
-        <v>0.555556</v>
+        <v>0.589552</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6176469999999999</v>
+        <v>0.464706</v>
       </c>
       <c r="M24" t="n">
-        <v>0.584958</v>
+        <v>0.519737</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,23 +2874,23 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_2.txt</t>
+          <t>_2_6_1_1790731720_17.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z24" t="n">
         <v>6</v>
       </c>
       <c r="AA24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2904,7 +2904,7 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.199885</v>
+        <v>0.191102</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.50828</v>
+        <v>0.545588</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6253919999999999</v>
+        <v>0.581505</v>
       </c>
       <c r="I25" t="n">
-        <v>0.560787</v>
+        <v>0.562974</v>
       </c>
       <c r="J25" t="n">
-        <v>0.201084</v>
+        <v>0.193516</v>
       </c>
       <c r="K25" t="n">
-        <v>0.536842</v>
+        <v>0.590909</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6</v>
+        <v>0.535294</v>
       </c>
       <c r="M25" t="n">
-        <v>0.566667</v>
+        <v>0.561728</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_5.txt</t>
+          <t>_2_6_1_1790731720_19.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3005,42 +3005,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.193022</v>
+        <v>0.20234</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E26" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.523632</v>
+        <v>0.490223</v>
       </c>
       <c r="H26" t="n">
-        <v>0.659875</v>
+        <v>0.550157</v>
       </c>
       <c r="I26" t="n">
-        <v>0.583911</v>
+        <v>0.518464</v>
       </c>
       <c r="J26" t="n">
-        <v>0.191672</v>
+        <v>0.204362</v>
       </c>
       <c r="K26" t="n">
-        <v>0.565657</v>
+        <v>0.533708</v>
       </c>
       <c r="L26" t="n">
-        <v>0.658824</v>
+        <v>0.558824</v>
       </c>
       <c r="M26" t="n">
-        <v>0.608696</v>
+        <v>0.545977</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,23 +3076,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_3.txt</t>
+          <t>_2_3_3_1_1790731769_19.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>6</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.192426</v>
+        <v>0.188807</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3123,25 +3123,25 @@
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6192</v>
+        <v>0.611006</v>
       </c>
       <c r="H27" t="n">
-        <v>0.606583</v>
+        <v>0.504702</v>
       </c>
       <c r="I27" t="n">
-        <v>0.612827</v>
+        <v>0.55279</v>
       </c>
       <c r="J27" t="n">
-        <v>0.196411</v>
+        <v>0.187855</v>
       </c>
       <c r="K27" t="n">
-        <v>0.641026</v>
+        <v>0.5923079999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.588235</v>
+        <v>0.452941</v>
       </c>
       <c r="M27" t="n">
-        <v>0.613497</v>
+        <v>0.513333</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_8.txt</t>
+          <t>_2_6_1_1790731720_2.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3207,7 +3207,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.188807</v>
+        <v>0.190124</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.611006</v>
+        <v>0.598604</v>
       </c>
       <c r="H28" t="n">
-        <v>0.504702</v>
+        <v>0.537618</v>
       </c>
       <c r="I28" t="n">
-        <v>0.55279</v>
+        <v>0.566474</v>
       </c>
       <c r="J28" t="n">
-        <v>0.187855</v>
+        <v>0.19043</v>
       </c>
       <c r="K28" t="n">
-        <v>0.5923079999999999</v>
+        <v>0.594406</v>
       </c>
       <c r="L28" t="n">
-        <v>0.452941</v>
+        <v>0.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0.513333</v>
+        <v>0.543131</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_2.txt</t>
+          <t>_2_6_1_1790731720_0.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.213079</v>
+        <v>0.205707</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3325,25 +3325,25 @@
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.499069</v>
+        <v>0.472464</v>
       </c>
       <c r="H29" t="n">
-        <v>0.420063</v>
+        <v>0.510972</v>
       </c>
       <c r="I29" t="n">
-        <v>0.45617</v>
+        <v>0.490964</v>
       </c>
       <c r="J29" t="n">
-        <v>0.215386</v>
+        <v>0.208808</v>
       </c>
       <c r="K29" t="n">
-        <v>0.511278</v>
+        <v>0.50303</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4</v>
+        <v>0.488235</v>
       </c>
       <c r="M29" t="n">
-        <v>0.448845</v>
+        <v>0.495522</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_10.txt</t>
+          <t>_2_3_3_1_1790731769_7.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3409,42 +3409,42 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.192818</v>
+        <v>0.188288</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E30" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.603101</v>
+        <v>0.549412</v>
       </c>
       <c r="H30" t="n">
-        <v>0.609718</v>
+        <v>0.731975</v>
       </c>
       <c r="I30" t="n">
-        <v>0.606391</v>
+        <v>0.627688</v>
       </c>
       <c r="J30" t="n">
-        <v>0.197291</v>
+        <v>0.188066</v>
       </c>
       <c r="K30" t="n">
-        <v>0.613924</v>
+        <v>0.59434</v>
       </c>
       <c r="L30" t="n">
-        <v>0.570588</v>
+        <v>0.7411759999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.591463</v>
+        <v>0.659686</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,23 +3480,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_10.txt</t>
+          <t>_2_3_3_1_1790731769_3.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>6</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3510,42 +3510,42 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.189554</v>
+        <v>0.193349</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E31" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F31" t="n">
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.608365</v>
+        <v>0.528325</v>
       </c>
       <c r="H31" t="n">
-        <v>0.501567</v>
+        <v>0.672414</v>
       </c>
       <c r="I31" t="n">
-        <v>0.549828</v>
+        <v>0.591724</v>
       </c>
       <c r="J31" t="n">
-        <v>0.188286</v>
+        <v>0.19347</v>
       </c>
       <c r="K31" t="n">
-        <v>0.601562</v>
+        <v>0.5612239999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>0.452941</v>
+        <v>0.6470590000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0.516779</v>
+        <v>0.601093</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,23 +3581,23 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_16.txt</t>
+          <t>_2_3_3_1_1790731769_0.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z31" t="n">
         <v>6</v>
       </c>
       <c r="AA31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3611,42 +3611,42 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.188427</v>
+        <v>0.194461</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E32" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.604356</v>
+        <v>0.52381</v>
       </c>
       <c r="H32" t="n">
-        <v>0.521944</v>
+        <v>0.637931</v>
       </c>
       <c r="I32" t="n">
-        <v>0.560135</v>
+        <v>0.575265</v>
       </c>
       <c r="J32" t="n">
-        <v>0.186991</v>
+        <v>0.196644</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6</v>
+        <v>0.555556</v>
       </c>
       <c r="L32" t="n">
-        <v>0.494118</v>
+        <v>0.6176469999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>0.541936</v>
+        <v>0.584958</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,23 +3682,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_1.txt</t>
+          <t>_2_3_3_1_1790731769_2.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>6</v>
       </c>
       <c r="AA32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3712,42 +3712,42 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.191088</v>
+        <v>0.189554</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1790731769</v>
+        <v>1790731720</v>
       </c>
       <c r="E33" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.548159</v>
+        <v>0.608365</v>
       </c>
       <c r="H33" t="n">
-        <v>0.606583</v>
+        <v>0.501567</v>
       </c>
       <c r="I33" t="n">
-        <v>0.575893</v>
+        <v>0.549828</v>
       </c>
       <c r="J33" t="n">
-        <v>0.194727</v>
+        <v>0.188286</v>
       </c>
       <c r="K33" t="n">
-        <v>0.569767</v>
+        <v>0.601562</v>
       </c>
       <c r="L33" t="n">
-        <v>0.576471</v>
+        <v>0.452941</v>
       </c>
       <c r="M33" t="n">
-        <v>0.573099</v>
+        <v>0.516779</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,23 +3783,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_9.txt</t>
+          <t>_2_6_1_1790731720_16.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z33" t="n">
         <v>6</v>
       </c>
       <c r="AA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -3813,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.209498</v>
+        <v>0.202863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3830,25 +3830,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.494078</v>
+        <v>0.517451</v>
       </c>
       <c r="H34" t="n">
-        <v>0.45768</v>
+        <v>0.534483</v>
       </c>
       <c r="I34" t="n">
-        <v>0.475183</v>
+        <v>0.525829</v>
       </c>
       <c r="J34" t="n">
-        <v>0.208328</v>
+        <v>0.203493</v>
       </c>
       <c r="K34" t="n">
-        <v>0.528169</v>
+        <v>0.541401</v>
       </c>
       <c r="L34" t="n">
-        <v>0.441176</v>
+        <v>0.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0.480769</v>
+        <v>0.519878</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_17.txt</t>
+          <t>_2_3_3_1_1790731769_1.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.202863</v>
+        <v>0.19965</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3931,25 +3931,25 @@
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.517451</v>
+        <v>0.501992</v>
       </c>
       <c r="H35" t="n">
-        <v>0.534483</v>
+        <v>0.592476</v>
       </c>
       <c r="I35" t="n">
-        <v>0.525829</v>
+        <v>0.543494</v>
       </c>
       <c r="J35" t="n">
-        <v>0.203493</v>
+        <v>0.201776</v>
       </c>
       <c r="K35" t="n">
-        <v>0.541401</v>
+        <v>0.5251400000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>0.552941</v>
       </c>
       <c r="M35" t="n">
-        <v>0.519878</v>
+        <v>0.538682</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_1.txt</t>
+          <t>_2_3_3_1_1790731769_18.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4015,7 +4015,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.196115</v>
+        <v>0.192818</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4032,25 +4032,25 @@
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.542222</v>
+        <v>0.603101</v>
       </c>
       <c r="H36" t="n">
-        <v>0.573668</v>
+        <v>0.609718</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5575020000000001</v>
+        <v>0.606391</v>
       </c>
       <c r="J36" t="n">
-        <v>0.194178</v>
+        <v>0.197291</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5786520000000001</v>
+        <v>0.613924</v>
       </c>
       <c r="L36" t="n">
-        <v>0.605882</v>
+        <v>0.570588</v>
       </c>
       <c r="M36" t="n">
-        <v>0.591954</v>
+        <v>0.591463</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_13.txt</t>
+          <t>_2_6_1_1790731720_10.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4116,42 +4116,42 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.192575</v>
+        <v>0.20802</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E37" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F37" t="n">
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.564912</v>
+        <v>0.475232</v>
       </c>
       <c r="H37" t="n">
-        <v>0.504702</v>
+        <v>0.481191</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5331129999999999</v>
+        <v>0.478193</v>
       </c>
       <c r="J37" t="n">
-        <v>0.191473</v>
+        <v>0.211148</v>
       </c>
       <c r="K37" t="n">
-        <v>0.613139</v>
+        <v>0.516556</v>
       </c>
       <c r="L37" t="n">
-        <v>0.494118</v>
+        <v>0.458824</v>
       </c>
       <c r="M37" t="n">
-        <v>0.547231</v>
+        <v>0.485981</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,23 +4187,23 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_18.txt</t>
+          <t>_2_3_3_1_1790731769_5.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z37" t="n">
         <v>6</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.205707</v>
+        <v>0.179242</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4234,25 +4234,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.472464</v>
+        <v>0.56259</v>
       </c>
       <c r="H38" t="n">
-        <v>0.510972</v>
+        <v>0.612853</v>
       </c>
       <c r="I38" t="n">
-        <v>0.490964</v>
+        <v>0.586647</v>
       </c>
       <c r="J38" t="n">
-        <v>0.208808</v>
+        <v>0.181026</v>
       </c>
       <c r="K38" t="n">
-        <v>0.50303</v>
+        <v>0.562874</v>
       </c>
       <c r="L38" t="n">
-        <v>0.488235</v>
+        <v>0.552941</v>
       </c>
       <c r="M38" t="n">
-        <v>0.495522</v>
+        <v>0.557864</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_7.txt</t>
+          <t>_2_3_3_1_1790731769_8.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4318,7 +4318,7 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.212559</v>
+        <v>0.199613</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4335,25 +4335,25 @@
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.507168</v>
+        <v>0.526536</v>
       </c>
       <c r="H39" t="n">
-        <v>0.443574</v>
+        <v>0.590909</v>
       </c>
       <c r="I39" t="n">
-        <v>0.473244</v>
+        <v>0.556868</v>
       </c>
       <c r="J39" t="n">
-        <v>0.214107</v>
+        <v>0.201073</v>
       </c>
       <c r="K39" t="n">
-        <v>0.522388</v>
+        <v>0.556818</v>
       </c>
       <c r="L39" t="n">
-        <v>0.411765</v>
+        <v>0.576471</v>
       </c>
       <c r="M39" t="n">
-        <v>0.460526</v>
+        <v>0.566474</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790731769_16.txt</t>
+          <t>_2_3_3_1_1790731769_12.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.191455</v>
+        <v>0.192575</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4436,25 +4436,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.534629</v>
+        <v>0.564912</v>
       </c>
       <c r="H40" t="n">
-        <v>0.689655</v>
+        <v>0.504702</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6023269999999999</v>
+        <v>0.5331129999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.190092</v>
+        <v>0.191473</v>
       </c>
       <c r="K40" t="n">
-        <v>0.576355</v>
+        <v>0.613139</v>
       </c>
       <c r="L40" t="n">
-        <v>0.688235</v>
+        <v>0.494118</v>
       </c>
       <c r="M40" t="n">
-        <v>0.627346</v>
+        <v>0.547231</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_11.txt</t>
+          <t>_2_6_1_1790731720_18.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.189438</v>
+        <v>0.19791</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790731720</v>
+        <v>1790731769</v>
       </c>
       <c r="E41" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.608939</v>
+        <v>0.494695</v>
       </c>
       <c r="H41" t="n">
-        <v>0.512539</v>
+        <v>0.584639</v>
       </c>
       <c r="I41" t="n">
-        <v>0.556596</v>
+        <v>0.535919</v>
       </c>
       <c r="J41" t="n">
-        <v>0.188568</v>
+        <v>0.197199</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5954199999999999</v>
+        <v>0.535519</v>
       </c>
       <c r="L41" t="n">
-        <v>0.458824</v>
+        <v>0.576471</v>
       </c>
       <c r="M41" t="n">
-        <v>0.518272</v>
+        <v>0.555241</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_6_1_1790731720_6.txt</t>
+          <t>_2_3_3_1_1790731769_11.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.5336891500000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0567295982908347</v>
+        <v>0.05672959829083467</v>
       </c>
       <c r="D2" t="n">
         <v>0.659686</v>
@@ -4710,7 +4710,7 @@
         <v>0.5559862499999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0370853153813502</v>
+        <v>0.03708531538135019</v>
       </c>
       <c r="D3" t="n">
         <v>0.627346</v>
